--- a/frontend/public/templates/prekes_sablonas.xlsx
+++ b/frontend/public/templates/prekes_sablonas.xlsx
@@ -34,7 +34,7 @@
     <t>preke_paslauga_kodas</t>
   </si>
   <si>
-    <t>1 - jei preke; 2 - jei paslauga, 3 - jei kodas</t>
+    <t xml:space="preserve">1 - jei preke; 2 - jei paslauga, 3 - jei kodas (PVM klasifikatorius kaip prekei), 4 - jei kodas (PVM klasifikatorius kaip paslaugai) </t>
   </si>
 </sst>
 </file>

--- a/frontend/public/templates/prekes_sablonas.xlsx
+++ b/frontend/public/templates/prekes_sablonas.xlsx
@@ -31,10 +31,10 @@
     <t>prekes_kodas*</t>
   </si>
   <si>
-    <t>preke_paslauga_kodas</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - jei preke; 2 - jei paslauga, 3 - jei kodas (PVM klasifikatorius kaip prekei), 4 - jei kodas (PVM klasifikatorius kaip paslaugai) </t>
+  </si>
+  <si>
+    <t>preke_paslauga_kodas* (galimos reikšmės: 1, 2, 3, 4)</t>
   </si>
 </sst>
 </file>
@@ -391,7 +391,7 @@
     <col min="1" max="1" width="33.3125" customWidth="1"/>
     <col min="2" max="2" width="17.83984375" customWidth="1"/>
     <col min="3" max="3" width="32.47265625" customWidth="1"/>
-    <col min="4" max="4" width="33.578125" customWidth="1"/>
+    <col min="4" max="4" width="43.62890625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -405,7 +405,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -419,7 +419,7 @@
         <v>123456789</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/templates/prekes_sablonas.xlsx
+++ b/frontend/public/templates/prekes_sablonas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>prekes_barkodas</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t>preke_paslauga_kodas* (galimos reikšmės: 1, 2, 3, 4)</t>
+  </si>
+  <si>
+    <t>mato_vnt</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -385,16 +391,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="33.3125" customWidth="1"/>
     <col min="2" max="2" width="17.83984375" customWidth="1"/>
     <col min="3" max="3" width="32.47265625" customWidth="1"/>
-    <col min="4" max="4" width="43.62890625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="43.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -405,10 +412,13 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -419,6 +429,9 @@
         <v>123456789</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
